--- a/resources/templates/Checklist_Positions/Template_T1(HUMSS).xlsx
+++ b/resources/templates/Checklist_Positions/Template_T1(HUMSS).xlsx
@@ -1029,7 +1029,7 @@
     <t>Recommended:</t>
   </si>
   <si>
-    <t>MA. CORAZON P. FEDEROSO</t>
+    <t>${encoder_name}</t>
   </si>
   <si>
     <t>RONALD KEVIN C. DEL ROSARIO</t>
@@ -1038,7 +1038,7 @@
     <t>VERNA C. CABAYA</t>
   </si>
   <si>
-    <t>Administrative Assistant III</t>
+    <t>${user_position}</t>
   </si>
   <si>
     <t>Administrative Officer IV-HR</t>
@@ -1047,7 +1047,7 @@
     <t>Administrative Officer V</t>
   </si>
   <si>
-    <t>Date: February 26, 2025</t>
+    <t>Date: ${date_of_signing}</t>
   </si>
   <si>
     <t>APC Form - (Revised 2018)</t>
@@ -2544,7 +2544,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2874,12 +2874,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4429,7 +4423,7 @@
       <c r="C11" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="244" t="s">
+      <c r="D11" s="242" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="59"/>
@@ -4454,11 +4448,11 @@
       <c r="C12" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="245" t="s">
+      <c r="D12" s="243" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="67"/>
-      <c r="F12" s="246" t="s">
+      <c r="F12" s="244" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="69"/>
@@ -4473,11 +4467,11 @@
       <c r="C13" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="245" t="s">
+      <c r="D13" s="243" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="67"/>
-      <c r="F13" s="246" t="s">
+      <c r="F13" s="244" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="69"/>
@@ -4492,7 +4486,7 @@
       <c r="C14" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="245" t="s">
+      <c r="D14" s="243" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="66"/>
@@ -4571,7 +4565,7 @@
       <c r="C19" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="247" t="s">
+      <c r="D19" s="245" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="84"/>
@@ -4692,7 +4686,7 @@
         <v>47</v>
       </c>
       <c r="D27" s="102"/>
-      <c r="E27" s="248" t="s">
+      <c r="E27" s="246" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="103" t="s">
@@ -4709,7 +4703,7 @@
         <v>49</v>
       </c>
       <c r="D28" s="107"/>
-      <c r="E28" s="247" t="s">
+      <c r="E28" s="245" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="85" t="s">
@@ -4727,7 +4721,7 @@
       <c r="C29" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="249" t="s">
+      <c r="D29" s="247" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="111"/>
@@ -4763,26 +4757,26 @@
       <c r="C31" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="249" t="s">
+      <c r="D31" s="247" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="111"/>
-      <c r="F31" s="119" t="s">
+      <c r="F31" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="G31" s="119"/>
-      <c r="H31" s="119"/>
-      <c r="I31" s="120"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="113"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="24" customHeight="1" spans="1:9">
       <c r="A32" s="88"/>
-      <c r="B32" s="121">
+      <c r="B32" s="119">
         <v>11</v>
       </c>
-      <c r="C32" s="122" t="s">
+      <c r="C32" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="249" t="s">
+      <c r="D32" s="247" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="110"/>
@@ -4802,25 +4796,25 @@
         <v>57</v>
       </c>
       <c r="D33" s="110"/>
-      <c r="E33" s="249" t="s">
+      <c r="E33" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="250" t="s">
+      <c r="F33" s="248" t="s">
         <v>34</v>
       </c>
-      <c r="G33" s="124"/>
-      <c r="H33" s="124"/>
-      <c r="I33" s="125"/>
+      <c r="G33" s="122"/>
+      <c r="H33" s="122"/>
+      <c r="I33" s="123"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="34.2" spans="1:10">
       <c r="A34" s="88"/>
       <c r="B34" s="114">
         <v>13</v>
       </c>
-      <c r="C34" s="126" t="s">
+      <c r="C34" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="249" t="s">
+      <c r="D34" s="247" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="110"/>
@@ -4831,33 +4825,33 @@
     </row>
     <row r="35" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:10">
       <c r="A35" s="88"/>
-      <c r="B35" s="127">
+      <c r="B35" s="125">
         <v>14</v>
       </c>
-      <c r="C35" s="128" t="s">
+      <c r="C35" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="251" t="s">
+      <c r="D35" s="249" t="s">
         <v>25</v>
       </c>
-      <c r="E35" s="129"/>
-      <c r="F35" s="130"/>
-      <c r="G35" s="131"/>
-      <c r="H35" s="131"/>
-      <c r="I35" s="132"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="128"/>
+      <c r="G35" s="129"/>
+      <c r="H35" s="129"/>
+      <c r="I35" s="130"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="24.95" customHeight="1" spans="1:10">
-      <c r="A36" s="133"/>
-      <c r="B36" s="134"/>
+      <c r="A36" s="131"/>
+      <c r="B36" s="132"/>
       <c r="C36" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="135"/>
-      <c r="E36" s="135"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="137"/>
-      <c r="H36" s="137"/>
-      <c r="I36" s="138"/>
+      <c r="D36" s="133"/>
+      <c r="E36" s="133"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="136"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="12" customHeight="1" spans="1:10">
       <c r="A37" s="39" t="s">
@@ -4869,752 +4863,752 @@
       <c r="C37" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="129" t="s">
+      <c r="D37" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="129"/>
-      <c r="F37" s="139"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="141"/>
+      <c r="E37" s="127"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="138"/>
+      <c r="H37" s="138"/>
+      <c r="I37" s="139"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="40.5" customHeight="1" spans="1:10">
-      <c r="A38" s="142"/>
+      <c r="A38" s="140"/>
       <c r="B38" s="100"/>
-      <c r="C38" s="143" t="s">
+      <c r="C38" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="135"/>
-      <c r="E38" s="135"/>
-      <c r="F38" s="144"/>
-      <c r="G38" s="145"/>
-      <c r="H38" s="145"/>
-      <c r="I38" s="146"/>
+      <c r="D38" s="133"/>
+      <c r="E38" s="133"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="143"/>
+      <c r="H38" s="143"/>
+      <c r="I38" s="144"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="33" customHeight="1" spans="1:10">
-      <c r="A39" s="142"/>
+      <c r="A39" s="140"/>
       <c r="B39" s="105"/>
-      <c r="C39" s="147" t="s">
+      <c r="C39" s="145" t="s">
         <v>64</v>
       </c>
       <c r="D39" s="110"/>
-      <c r="E39" s="249" t="s">
+      <c r="E39" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F39" s="148"/>
-      <c r="G39" s="149"/>
-      <c r="H39" s="149"/>
-      <c r="I39" s="150"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148"/>
     </row>
     <row r="40" s="2" customFormat="1" ht="50.25" customHeight="1" spans="1:10">
       <c r="A40" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="151">
+      <c r="B40" s="149">
         <v>16</v>
       </c>
-      <c r="C40" s="152" t="s">
+      <c r="C40" s="150" t="s">
         <v>66</v>
       </c>
       <c r="D40" s="84"/>
-      <c r="E40" s="249" t="s">
+      <c r="E40" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F40" s="153"/>
-      <c r="G40" s="154"/>
-      <c r="H40" s="154"/>
-      <c r="I40" s="155"/>
-      <c r="J40" s="156"/>
+      <c r="F40" s="151"/>
+      <c r="G40" s="152"/>
+      <c r="H40" s="152"/>
+      <c r="I40" s="153"/>
+      <c r="J40" s="154"/>
     </row>
     <row r="41" s="2" customFormat="1" ht="24" customHeight="1" spans="1:10">
-      <c r="A41" s="142"/>
-      <c r="B41" s="157">
+      <c r="A41" s="140"/>
+      <c r="B41" s="155">
         <v>17</v>
       </c>
       <c r="C41" s="115" t="s">
         <v>67</v>
       </c>
       <c r="D41" s="111"/>
-      <c r="E41" s="249" t="s">
+      <c r="E41" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F41" s="153"/>
-      <c r="G41" s="154"/>
-      <c r="H41" s="154"/>
-      <c r="I41" s="155"/>
+      <c r="F41" s="151"/>
+      <c r="G41" s="152"/>
+      <c r="H41" s="152"/>
+      <c r="I41" s="153"/>
     </row>
     <row r="42" s="2" customFormat="1" ht="12" customHeight="1" spans="1:10">
-      <c r="A42" s="142"/>
-      <c r="B42" s="158">
+      <c r="A42" s="140"/>
+      <c r="B42" s="156">
         <v>18</v>
       </c>
       <c r="C42" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="159"/>
-      <c r="E42" s="160"/>
-      <c r="F42" s="161"/>
-      <c r="G42" s="162"/>
-      <c r="H42" s="162"/>
-      <c r="I42" s="163"/>
+      <c r="D42" s="157"/>
+      <c r="E42" s="158"/>
+      <c r="F42" s="159"/>
+      <c r="G42" s="160"/>
+      <c r="H42" s="160"/>
+      <c r="I42" s="161"/>
     </row>
     <row r="43" s="2" customFormat="1" ht="27.75" customHeight="1" spans="1:10">
-      <c r="A43" s="142"/>
-      <c r="B43" s="164"/>
-      <c r="C43" s="147" t="s">
+      <c r="A43" s="140"/>
+      <c r="B43" s="162"/>
+      <c r="C43" s="145" t="s">
         <v>69</v>
       </c>
       <c r="D43" s="84"/>
-      <c r="E43" s="249" t="s">
+      <c r="E43" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="165"/>
-      <c r="G43" s="166"/>
-      <c r="H43" s="166"/>
-      <c r="I43" s="167"/>
+      <c r="F43" s="163"/>
+      <c r="G43" s="164"/>
+      <c r="H43" s="164"/>
+      <c r="I43" s="165"/>
     </row>
     <row r="44" s="2" customFormat="1" ht="12" customHeight="1" spans="1:10">
-      <c r="A44" s="142"/>
-      <c r="B44" s="168">
+      <c r="A44" s="140"/>
+      <c r="B44" s="166">
         <v>19</v>
       </c>
-      <c r="C44" s="122" t="s">
+      <c r="C44" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="D44" s="159"/>
-      <c r="E44" s="160"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="140"/>
-      <c r="H44" s="140"/>
-      <c r="I44" s="141"/>
+      <c r="D44" s="157"/>
+      <c r="E44" s="158"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="138"/>
+      <c r="H44" s="138"/>
+      <c r="I44" s="139"/>
     </row>
     <row r="45" s="2" customFormat="1" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="142"/>
-      <c r="B45" s="169"/>
-      <c r="C45" s="143" t="s">
+      <c r="A45" s="140"/>
+      <c r="B45" s="167"/>
+      <c r="C45" s="141" t="s">
         <v>71</v>
       </c>
       <c r="D45" s="110"/>
-      <c r="E45" s="249" t="s">
+      <c r="E45" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F45" s="144"/>
-      <c r="G45" s="145"/>
-      <c r="H45" s="145"/>
-      <c r="I45" s="146"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="143"/>
+      <c r="I45" s="144"/>
     </row>
     <row r="46" s="2" customFormat="1" ht="24" customHeight="1" spans="1:10">
-      <c r="A46" s="142"/>
-      <c r="B46" s="170"/>
-      <c r="C46" s="171" t="s">
+      <c r="A46" s="140"/>
+      <c r="B46" s="168"/>
+      <c r="C46" s="169" t="s">
         <v>72</v>
       </c>
       <c r="D46" s="110"/>
-      <c r="E46" s="249" t="s">
+      <c r="E46" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F46" s="148"/>
-      <c r="G46" s="149"/>
-      <c r="H46" s="149"/>
-      <c r="I46" s="150"/>
+      <c r="F46" s="146"/>
+      <c r="G46" s="147"/>
+      <c r="H46" s="147"/>
+      <c r="I46" s="148"/>
     </row>
     <row r="47" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A47" s="142"/>
-      <c r="B47" s="158">
+      <c r="A47" s="140"/>
+      <c r="B47" s="156">
         <v>20</v>
       </c>
-      <c r="C47" s="172" t="s">
+      <c r="C47" s="170" t="s">
         <v>73</v>
       </c>
       <c r="D47" s="95"/>
-      <c r="E47" s="129" t="s">
+      <c r="E47" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="139" t="s">
+      <c r="F47" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="140"/>
-      <c r="H47" s="140"/>
-      <c r="I47" s="141"/>
+      <c r="G47" s="138"/>
+      <c r="H47" s="138"/>
+      <c r="I47" s="139"/>
     </row>
     <row r="48" s="2" customFormat="1" ht="22.8" spans="1:10">
-      <c r="A48" s="142"/>
-      <c r="B48" s="164"/>
-      <c r="C48" s="147" t="s">
+      <c r="A48" s="140"/>
+      <c r="B48" s="162"/>
+      <c r="C48" s="145" t="s">
         <v>74</v>
       </c>
       <c r="D48" s="107"/>
-      <c r="E48" s="135"/>
-      <c r="F48" s="148"/>
-      <c r="G48" s="149"/>
-      <c r="H48" s="149"/>
-      <c r="I48" s="150"/>
+      <c r="E48" s="133"/>
+      <c r="F48" s="146"/>
+      <c r="G48" s="147"/>
+      <c r="H48" s="147"/>
+      <c r="I48" s="148"/>
     </row>
     <row r="49" s="2" customFormat="1" ht="48.75" customHeight="1" spans="1:9">
       <c r="A49" s="47"/>
-      <c r="B49" s="164">
+      <c r="B49" s="162">
         <v>21</v>
       </c>
-      <c r="C49" s="173" t="s">
+      <c r="C49" s="171" t="s">
         <v>75</v>
       </c>
       <c r="D49" s="110"/>
-      <c r="E49" s="249" t="s">
+      <c r="E49" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F49" s="153" t="s">
+      <c r="F49" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="G49" s="154"/>
-      <c r="H49" s="154"/>
-      <c r="I49" s="155"/>
+      <c r="G49" s="152"/>
+      <c r="H49" s="152"/>
+      <c r="I49" s="153"/>
     </row>
     <row r="50" s="2" customFormat="1" ht="35.25" customHeight="1" spans="1:9">
       <c r="A50" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="B50" s="174">
+      <c r="B50" s="172">
         <v>22</v>
       </c>
       <c r="C50" s="115" t="s">
         <v>77</v>
       </c>
       <c r="D50" s="110"/>
-      <c r="E50" s="249" t="s">
+      <c r="E50" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F50" s="153" t="s">
+      <c r="F50" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="154"/>
-      <c r="H50" s="154"/>
-      <c r="I50" s="155"/>
+      <c r="G50" s="152"/>
+      <c r="H50" s="152"/>
+      <c r="I50" s="153"/>
     </row>
     <row r="51" s="2" customFormat="1" ht="42" customHeight="1" spans="1:9">
-      <c r="A51" s="142"/>
-      <c r="B51" s="151">
+      <c r="A51" s="140"/>
+      <c r="B51" s="149">
         <v>23</v>
       </c>
-      <c r="C51" s="175" t="s">
+      <c r="C51" s="173" t="s">
         <v>78</v>
       </c>
       <c r="D51" s="110"/>
-      <c r="E51" s="249" t="s">
+      <c r="E51" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="F51" s="176" t="s">
+      <c r="F51" s="174" t="s">
         <v>34</v>
       </c>
-      <c r="G51" s="177"/>
-      <c r="H51" s="177"/>
-      <c r="I51" s="178"/>
+      <c r="G51" s="175"/>
+      <c r="H51" s="175"/>
+      <c r="I51" s="176"/>
     </row>
     <row r="52" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A52" s="142"/>
-      <c r="B52" s="179">
+      <c r="A52" s="140"/>
+      <c r="B52" s="177">
         <v>24</v>
       </c>
-      <c r="C52" s="122" t="s">
+      <c r="C52" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="D52" s="159"/>
-      <c r="E52" s="160"/>
-      <c r="F52" s="180"/>
-      <c r="G52" s="181"/>
-      <c r="H52" s="181"/>
-      <c r="I52" s="182"/>
+      <c r="D52" s="157"/>
+      <c r="E52" s="158"/>
+      <c r="F52" s="178"/>
+      <c r="G52" s="179"/>
+      <c r="H52" s="179"/>
+      <c r="I52" s="180"/>
     </row>
     <row r="53" s="2" customFormat="1" ht="33" customHeight="1" spans="1:9">
-      <c r="A53" s="142"/>
-      <c r="B53" s="158"/>
-      <c r="C53" s="183" t="s">
+      <c r="A53" s="140"/>
+      <c r="B53" s="156"/>
+      <c r="C53" s="181" t="s">
         <v>80</v>
       </c>
       <c r="D53" s="110"/>
-      <c r="E53" s="184"/>
-      <c r="F53" s="144" t="s">
+      <c r="E53" s="182"/>
+      <c r="F53" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="G53" s="145"/>
-      <c r="H53" s="145"/>
-      <c r="I53" s="146"/>
+      <c r="G53" s="143"/>
+      <c r="H53" s="143"/>
+      <c r="I53" s="144"/>
     </row>
     <row r="54" s="2" customFormat="1" ht="23.25" customHeight="1" spans="1:9">
-      <c r="A54" s="142"/>
-      <c r="B54" s="158"/>
-      <c r="C54" s="183" t="s">
+      <c r="A54" s="140"/>
+      <c r="B54" s="156"/>
+      <c r="C54" s="181" t="s">
         <v>81</v>
       </c>
       <c r="D54" s="110"/>
-      <c r="E54" s="184"/>
-      <c r="F54" s="144"/>
-      <c r="G54" s="145"/>
-      <c r="H54" s="145"/>
-      <c r="I54" s="146"/>
+      <c r="E54" s="182"/>
+      <c r="F54" s="142"/>
+      <c r="G54" s="143"/>
+      <c r="H54" s="143"/>
+      <c r="I54" s="144"/>
     </row>
     <row r="55" s="2" customFormat="1" ht="34.5" customHeight="1" spans="1:9">
-      <c r="A55" s="142"/>
-      <c r="B55" s="158"/>
-      <c r="C55" s="183" t="s">
+      <c r="A55" s="140"/>
+      <c r="B55" s="156"/>
+      <c r="C55" s="181" t="s">
         <v>82</v>
       </c>
       <c r="D55" s="110"/>
-      <c r="E55" s="184"/>
-      <c r="F55" s="144"/>
-      <c r="G55" s="145"/>
-      <c r="H55" s="145"/>
-      <c r="I55" s="146"/>
+      <c r="E55" s="182"/>
+      <c r="F55" s="142"/>
+      <c r="G55" s="143"/>
+      <c r="H55" s="143"/>
+      <c r="I55" s="144"/>
     </row>
     <row r="56" s="2" customFormat="1" ht="36.75" customHeight="1" spans="1:9">
-      <c r="A56" s="142"/>
-      <c r="B56" s="158"/>
-      <c r="C56" s="183" t="s">
+      <c r="A56" s="140"/>
+      <c r="B56" s="156"/>
+      <c r="C56" s="181" t="s">
         <v>83</v>
       </c>
       <c r="D56" s="110"/>
-      <c r="E56" s="184"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="145"/>
-      <c r="H56" s="145"/>
-      <c r="I56" s="146"/>
+      <c r="E56" s="182"/>
+      <c r="F56" s="142"/>
+      <c r="G56" s="143"/>
+      <c r="H56" s="143"/>
+      <c r="I56" s="144"/>
     </row>
     <row r="57" s="2" customFormat="1" ht="40.5" customHeight="1" spans="1:9">
-      <c r="A57" s="142"/>
-      <c r="B57" s="158"/>
-      <c r="C57" s="183" t="s">
+      <c r="A57" s="140"/>
+      <c r="B57" s="156"/>
+      <c r="C57" s="181" t="s">
         <v>84</v>
       </c>
       <c r="D57" s="110"/>
-      <c r="E57" s="184"/>
-      <c r="F57" s="144"/>
-      <c r="G57" s="145"/>
-      <c r="H57" s="145"/>
-      <c r="I57" s="146"/>
+      <c r="E57" s="182"/>
+      <c r="F57" s="142"/>
+      <c r="G57" s="143"/>
+      <c r="H57" s="143"/>
+      <c r="I57" s="144"/>
     </row>
     <row r="58" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:9">
-      <c r="A58" s="142"/>
-      <c r="B58" s="164"/>
-      <c r="C58" s="173" t="s">
+      <c r="A58" s="140"/>
+      <c r="B58" s="162"/>
+      <c r="C58" s="171" t="s">
         <v>85</v>
       </c>
       <c r="D58" s="110"/>
-      <c r="E58" s="184"/>
-      <c r="F58" s="148"/>
-      <c r="G58" s="149"/>
-      <c r="H58" s="149"/>
-      <c r="I58" s="150"/>
+      <c r="E58" s="182"/>
+      <c r="F58" s="146"/>
+      <c r="G58" s="147"/>
+      <c r="H58" s="147"/>
+      <c r="I58" s="148"/>
     </row>
     <row r="59" s="2" customFormat="1" ht="15" customHeight="1" spans="1:9">
-      <c r="A59" s="142"/>
-      <c r="B59" s="158">
+      <c r="A59" s="140"/>
+      <c r="B59" s="156">
         <v>25</v>
       </c>
-      <c r="C59" s="183" t="s">
+      <c r="C59" s="181" t="s">
         <v>86</v>
       </c>
       <c r="D59" s="95"/>
-      <c r="E59" s="252" t="s">
+      <c r="E59" s="250" t="s">
         <v>25</v>
       </c>
-      <c r="F59" s="139" t="s">
+      <c r="F59" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="G59" s="140"/>
-      <c r="H59" s="140"/>
-      <c r="I59" s="141"/>
+      <c r="G59" s="138"/>
+      <c r="H59" s="138"/>
+      <c r="I59" s="139"/>
     </row>
     <row r="60" s="2" customFormat="1" ht="11.4" spans="1:9">
-      <c r="A60" s="142"/>
-      <c r="B60" s="185"/>
-      <c r="C60" s="183" t="s">
+      <c r="A60" s="140"/>
+      <c r="B60" s="183"/>
+      <c r="C60" s="181" t="s">
         <v>87</v>
       </c>
       <c r="D60" s="107"/>
       <c r="E60" s="107"/>
-      <c r="F60" s="144"/>
-      <c r="G60" s="145"/>
-      <c r="H60" s="145"/>
-      <c r="I60" s="146"/>
+      <c r="F60" s="142"/>
+      <c r="G60" s="143"/>
+      <c r="H60" s="143"/>
+      <c r="I60" s="144"/>
     </row>
     <row r="61" s="2" customFormat="1" ht="22.8" spans="1:9">
-      <c r="A61" s="142"/>
-      <c r="B61" s="185"/>
-      <c r="C61" s="143" t="s">
+      <c r="A61" s="140"/>
+      <c r="B61" s="183"/>
+      <c r="C61" s="141" t="s">
         <v>88</v>
       </c>
-      <c r="D61" s="186"/>
-      <c r="E61" s="247" t="s">
+      <c r="D61" s="184"/>
+      <c r="E61" s="245" t="s">
         <v>25</v>
       </c>
-      <c r="F61" s="144"/>
-      <c r="G61" s="145"/>
-      <c r="H61" s="145"/>
-      <c r="I61" s="146"/>
+      <c r="F61" s="142"/>
+      <c r="G61" s="143"/>
+      <c r="H61" s="143"/>
+      <c r="I61" s="144"/>
     </row>
     <row r="62" s="2" customFormat="1" ht="22.8" spans="1:9">
-      <c r="A62" s="142"/>
-      <c r="B62" s="187"/>
-      <c r="C62" s="143" t="s">
+      <c r="A62" s="140"/>
+      <c r="B62" s="185"/>
+      <c r="C62" s="141" t="s">
         <v>89</v>
       </c>
-      <c r="D62" s="186"/>
-      <c r="E62" s="247" t="s">
+      <c r="D62" s="184"/>
+      <c r="E62" s="245" t="s">
         <v>25</v>
       </c>
-      <c r="F62" s="148"/>
-      <c r="G62" s="149"/>
-      <c r="H62" s="149"/>
-      <c r="I62" s="150"/>
+      <c r="F62" s="146"/>
+      <c r="G62" s="147"/>
+      <c r="H62" s="147"/>
+      <c r="I62" s="148"/>
     </row>
     <row r="63" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:9">
-      <c r="A63" s="142"/>
-      <c r="B63" s="158">
+      <c r="A63" s="140"/>
+      <c r="B63" s="156">
         <v>26</v>
       </c>
-      <c r="C63" s="122" t="s">
+      <c r="C63" s="120" t="s">
         <v>90</v>
       </c>
       <c r="D63" s="95"/>
-      <c r="E63" s="252" t="s">
+      <c r="E63" s="250" t="s">
         <v>25</v>
       </c>
-      <c r="F63" s="139"/>
-      <c r="G63" s="140"/>
-      <c r="H63" s="140"/>
-      <c r="I63" s="141"/>
+      <c r="F63" s="137"/>
+      <c r="G63" s="138"/>
+      <c r="H63" s="138"/>
+      <c r="I63" s="139"/>
     </row>
     <row r="64" s="2" customFormat="1" ht="32.25" customHeight="1" spans="1:9">
-      <c r="A64" s="142"/>
-      <c r="B64" s="158"/>
-      <c r="C64" s="147" t="s">
+      <c r="A64" s="140"/>
+      <c r="B64" s="156"/>
+      <c r="C64" s="145" t="s">
         <v>91</v>
       </c>
       <c r="D64" s="107"/>
       <c r="E64" s="107"/>
-      <c r="F64" s="148"/>
-      <c r="G64" s="149"/>
-      <c r="H64" s="149"/>
-      <c r="I64" s="150"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="147"/>
+      <c r="H64" s="147"/>
+      <c r="I64" s="148"/>
     </row>
     <row r="65" s="2" customFormat="1" ht="37.5" customHeight="1" spans="1:9">
       <c r="A65" s="47"/>
-      <c r="B65" s="174">
+      <c r="B65" s="172">
         <v>27</v>
       </c>
-      <c r="C65" s="188" t="s">
+      <c r="C65" s="186" t="s">
         <v>92</v>
       </c>
       <c r="D65" s="84"/>
-      <c r="E65" s="247" t="s">
+      <c r="E65" s="245" t="s">
         <v>25</v>
       </c>
-      <c r="F65" s="153"/>
-      <c r="G65" s="154"/>
-      <c r="H65" s="154"/>
-      <c r="I65" s="155"/>
+      <c r="F65" s="151"/>
+      <c r="G65" s="152"/>
+      <c r="H65" s="152"/>
+      <c r="I65" s="153"/>
     </row>
     <row r="66" s="2" customFormat="1" ht="34.2" spans="1:9">
       <c r="A66" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="189">
+      <c r="B66" s="187">
         <v>28</v>
       </c>
-      <c r="C66" s="173" t="s">
+      <c r="C66" s="171" t="s">
         <v>94</v>
       </c>
-      <c r="D66" s="253" t="s">
+      <c r="D66" s="251" t="s">
         <v>25</v>
       </c>
-      <c r="E66" s="191"/>
-      <c r="F66" s="153"/>
-      <c r="G66" s="154"/>
-      <c r="H66" s="154"/>
-      <c r="I66" s="155"/>
+      <c r="E66" s="189"/>
+      <c r="F66" s="151"/>
+      <c r="G66" s="152"/>
+      <c r="H66" s="152"/>
+      <c r="I66" s="153"/>
     </row>
     <row r="67" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A67" s="142"/>
-      <c r="B67" s="192">
+      <c r="A67" s="140"/>
+      <c r="B67" s="190">
         <v>29</v>
       </c>
-      <c r="C67" s="193" t="s">
+      <c r="C67" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="D67" s="253" t="s">
+      <c r="D67" s="251" t="s">
         <v>25</v>
       </c>
-      <c r="E67" s="190"/>
-      <c r="F67" s="153"/>
-      <c r="G67" s="154"/>
-      <c r="H67" s="154"/>
-      <c r="I67" s="155"/>
+      <c r="E67" s="188"/>
+      <c r="F67" s="151"/>
+      <c r="G67" s="152"/>
+      <c r="H67" s="152"/>
+      <c r="I67" s="153"/>
     </row>
     <row r="68" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A68" s="142"/>
-      <c r="B68" s="192">
+      <c r="A68" s="140"/>
+      <c r="B68" s="190">
         <v>30</v>
       </c>
-      <c r="C68" s="193" t="s">
+      <c r="C68" s="191" t="s">
         <v>96</v>
       </c>
-      <c r="D68" s="253" t="s">
+      <c r="D68" s="251" t="s">
         <v>25</v>
       </c>
-      <c r="E68" s="190"/>
-      <c r="F68" s="153"/>
-      <c r="G68" s="154"/>
-      <c r="H68" s="154"/>
-      <c r="I68" s="155"/>
+      <c r="E68" s="188"/>
+      <c r="F68" s="151"/>
+      <c r="G68" s="152"/>
+      <c r="H68" s="152"/>
+      <c r="I68" s="153"/>
     </row>
     <row r="69" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A69" s="142"/>
-      <c r="B69" s="192">
+      <c r="A69" s="140"/>
+      <c r="B69" s="190">
         <v>31</v>
       </c>
       <c r="C69" s="115" t="s">
         <v>97</v>
       </c>
-      <c r="D69" s="253" t="s">
+      <c r="D69" s="251" t="s">
         <v>25</v>
       </c>
-      <c r="E69" s="190"/>
-      <c r="F69" s="153"/>
-      <c r="G69" s="154"/>
-      <c r="H69" s="154"/>
-      <c r="I69" s="155"/>
+      <c r="E69" s="188"/>
+      <c r="F69" s="151"/>
+      <c r="G69" s="152"/>
+      <c r="H69" s="152"/>
+      <c r="I69" s="153"/>
     </row>
     <row r="70" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A70" s="142"/>
-      <c r="B70" s="192">
+      <c r="A70" s="140"/>
+      <c r="B70" s="190">
         <v>32</v>
       </c>
       <c r="C70" s="115" t="s">
         <v>98</v>
       </c>
-      <c r="D70" s="253" t="s">
+      <c r="D70" s="251" t="s">
         <v>25</v>
       </c>
       <c r="E70" s="111"/>
-      <c r="F70" s="153"/>
-      <c r="G70" s="154"/>
-      <c r="H70" s="154"/>
-      <c r="I70" s="155"/>
+      <c r="F70" s="151"/>
+      <c r="G70" s="152"/>
+      <c r="H70" s="152"/>
+      <c r="I70" s="153"/>
     </row>
     <row r="71" s="2" customFormat="1" ht="12" customHeight="1" spans="1:9">
-      <c r="A71" s="142"/>
-      <c r="B71" s="192">
+      <c r="A71" s="140"/>
+      <c r="B71" s="190">
         <v>33</v>
       </c>
-      <c r="C71" s="193" t="s">
+      <c r="C71" s="191" t="s">
         <v>99</v>
       </c>
       <c r="D71" s="111"/>
       <c r="E71" s="111"/>
-      <c r="F71" s="153" t="s">
+      <c r="F71" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="G71" s="154"/>
-      <c r="H71" s="154"/>
-      <c r="I71" s="155"/>
+      <c r="G71" s="152"/>
+      <c r="H71" s="152"/>
+      <c r="I71" s="153"/>
     </row>
     <row r="72" s="2" customFormat="1" ht="57" spans="1:9">
-      <c r="A72" s="142"/>
-      <c r="B72" s="194">
+      <c r="A72" s="140"/>
+      <c r="B72" s="192">
         <v>34</v>
       </c>
-      <c r="C72" s="195" t="s">
+      <c r="C72" s="193" t="s">
         <v>100</v>
       </c>
       <c r="D72" s="111"/>
       <c r="E72" s="111"/>
-      <c r="F72" s="153"/>
-      <c r="G72" s="154"/>
-      <c r="H72" s="154"/>
-      <c r="I72" s="155"/>
+      <c r="F72" s="151"/>
+      <c r="G72" s="152"/>
+      <c r="H72" s="152"/>
+      <c r="I72" s="153"/>
     </row>
     <row r="73" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A73" s="47"/>
-      <c r="B73" s="196">
+      <c r="B73" s="194">
         <v>35</v>
       </c>
-      <c r="C73" s="197" t="s">
+      <c r="C73" s="195" t="s">
         <v>101</v>
       </c>
-      <c r="D73" s="198"/>
-      <c r="E73" s="198"/>
-      <c r="F73" s="199"/>
-      <c r="G73" s="200"/>
-      <c r="H73" s="200"/>
-      <c r="I73" s="201"/>
+      <c r="D73" s="196"/>
+      <c r="E73" s="196"/>
+      <c r="F73" s="197"/>
+      <c r="G73" s="198"/>
+      <c r="H73" s="198"/>
+      <c r="I73" s="199"/>
     </row>
     <row r="74" s="2" customFormat="1" ht="12.15" spans="1:9">
-      <c r="A74" s="202" t="s">
+      <c r="A74" s="200" t="s">
         <v>102</v>
       </c>
-      <c r="B74" s="203"/>
-      <c r="C74" s="204"/>
-      <c r="D74" s="205"/>
-      <c r="E74" s="205"/>
-      <c r="F74" s="204"/>
-      <c r="G74" s="204"/>
-      <c r="H74" s="204"/>
-      <c r="I74" s="204"/>
+      <c r="B74" s="201"/>
+      <c r="C74" s="202"/>
+      <c r="D74" s="203"/>
+      <c r="E74" s="203"/>
+      <c r="F74" s="202"/>
+      <c r="G74" s="202"/>
+      <c r="H74" s="202"/>
+      <c r="I74" s="202"/>
     </row>
     <row r="75" s="2" customFormat="1" ht="3.75" customHeight="1" spans="1:9">
-      <c r="A75" s="206"/>
-      <c r="B75" s="207"/>
-      <c r="C75" s="208"/>
-      <c r="D75" s="209"/>
-      <c r="E75" s="209"/>
-      <c r="F75" s="209"/>
-      <c r="G75" s="209"/>
-      <c r="H75" s="209"/>
-      <c r="I75" s="210"/>
+      <c r="A75" s="204"/>
+      <c r="B75" s="205"/>
+      <c r="C75" s="206"/>
+      <c r="D75" s="207"/>
+      <c r="E75" s="207"/>
+      <c r="F75" s="207"/>
+      <c r="G75" s="207"/>
+      <c r="H75" s="207"/>
+      <c r="I75" s="208"/>
     </row>
     <row r="76" s="2" customFormat="1" ht="11.4" spans="1:9">
-      <c r="A76" s="211" t="s">
+      <c r="A76" s="209" t="s">
         <v>103</v>
       </c>
-      <c r="B76" s="212"/>
-      <c r="I76" s="213"/>
+      <c r="B76" s="210"/>
+      <c r="I76" s="211"/>
     </row>
     <row r="77" s="2" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A77" s="214" t="s">
+      <c r="A77" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="B77" s="203"/>
-      <c r="I77" s="213"/>
+      <c r="B77" s="201"/>
+      <c r="I77" s="211"/>
     </row>
     <row r="78" s="2" customFormat="1" ht="11.4" spans="1:9">
-      <c r="A78" s="214" t="s">
+      <c r="A78" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="B78" s="203"/>
-      <c r="C78" s="215"/>
-      <c r="D78" s="215"/>
-      <c r="E78" s="215"/>
-      <c r="F78" s="215"/>
-      <c r="G78" s="215"/>
-      <c r="H78" s="215"/>
-      <c r="I78" s="213"/>
+      <c r="B78" s="201"/>
+      <c r="C78" s="213"/>
+      <c r="D78" s="213"/>
+      <c r="E78" s="213"/>
+      <c r="F78" s="213"/>
+      <c r="G78" s="213"/>
+      <c r="H78" s="213"/>
+      <c r="I78" s="211"/>
     </row>
     <row r="79" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A79" s="216" t="s">
+      <c r="A79" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="B79" s="217"/>
-      <c r="F79" s="218"/>
-      <c r="G79" s="218"/>
-      <c r="H79" s="218"/>
-      <c r="I79" s="219"/>
+      <c r="B79" s="215"/>
+      <c r="F79" s="216"/>
+      <c r="G79" s="216"/>
+      <c r="H79" s="216"/>
+      <c r="I79" s="217"/>
     </row>
     <row r="80" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:9">
-      <c r="A80" s="216"/>
-      <c r="B80" s="203"/>
-      <c r="C80" s="203"/>
-      <c r="D80" s="203"/>
-      <c r="E80" s="203"/>
-      <c r="F80" s="203"/>
-      <c r="G80" s="203"/>
-      <c r="H80" s="203"/>
-      <c r="I80" s="213"/>
+      <c r="A80" s="214"/>
+      <c r="B80" s="201"/>
+      <c r="C80" s="201"/>
+      <c r="D80" s="201"/>
+      <c r="E80" s="201"/>
+      <c r="F80" s="201"/>
+      <c r="G80" s="201"/>
+      <c r="H80" s="201"/>
+      <c r="I80" s="211"/>
     </row>
     <row r="81" s="2" customFormat="1" ht="8.25" customHeight="1" spans="1:10">
-      <c r="A81" s="220"/>
-      <c r="B81" s="221"/>
-      <c r="C81" s="222"/>
-      <c r="D81" s="222"/>
-      <c r="E81" s="222"/>
-      <c r="F81" s="222"/>
-      <c r="G81" s="222"/>
-      <c r="H81" s="222"/>
-      <c r="I81" s="223"/>
+      <c r="A81" s="218"/>
+      <c r="B81" s="219"/>
+      <c r="C81" s="220"/>
+      <c r="D81" s="220"/>
+      <c r="E81" s="220"/>
+      <c r="F81" s="220"/>
+      <c r="G81" s="220"/>
+      <c r="H81" s="220"/>
+      <c r="I81" s="221"/>
     </row>
     <row r="82" s="2" customFormat="1" ht="11.4" spans="1:10">
-      <c r="A82" s="224" t="s">
+      <c r="A82" s="222" t="s">
         <v>107</v>
       </c>
-      <c r="B82" s="207"/>
-      <c r="C82" s="224" t="s">
+      <c r="B82" s="205"/>
+      <c r="C82" s="222" t="s">
         <v>108</v>
       </c>
-      <c r="D82" s="224" t="s">
+      <c r="D82" s="222" t="s">
         <v>109</v>
       </c>
-      <c r="E82" s="208"/>
-      <c r="F82" s="208"/>
-      <c r="G82" s="208"/>
-      <c r="H82" s="208"/>
-      <c r="I82" s="210"/>
+      <c r="E82" s="206"/>
+      <c r="F82" s="206"/>
+      <c r="G82" s="206"/>
+      <c r="H82" s="206"/>
+      <c r="I82" s="208"/>
     </row>
     <row r="83" s="2" customFormat="1" ht="9.75" customHeight="1" spans="1:10">
-      <c r="A83" s="216"/>
-      <c r="B83" s="203"/>
-      <c r="C83" s="225"/>
-      <c r="D83" s="225"/>
-      <c r="E83" s="226"/>
-      <c r="F83" s="226"/>
-      <c r="G83" s="226"/>
-      <c r="H83" s="226"/>
-      <c r="I83" s="227"/>
+      <c r="A83" s="214"/>
+      <c r="B83" s="201"/>
+      <c r="C83" s="223"/>
+      <c r="D83" s="223"/>
+      <c r="E83" s="224"/>
+      <c r="F83" s="224"/>
+      <c r="G83" s="224"/>
+      <c r="H83" s="224"/>
+      <c r="I83" s="225"/>
     </row>
     <row r="84" s="2" customFormat="1" ht="15" customHeight="1" spans="1:10">
-      <c r="A84" s="228" t="s">
+      <c r="A84" s="226" t="s">
         <v>110</v>
       </c>
-      <c r="B84" s="229"/>
-      <c r="C84" s="228" t="s">
+      <c r="B84" s="227"/>
+      <c r="C84" s="226" t="s">
         <v>111</v>
       </c>
-      <c r="D84" s="216"/>
-      <c r="E84" s="230" t="s">
+      <c r="D84" s="214"/>
+      <c r="E84" s="228" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="230"/>
-      <c r="G84" s="230"/>
-      <c r="H84" s="230"/>
-      <c r="I84" s="231"/>
-      <c r="J84" s="232"/>
+      <c r="F84" s="228"/>
+      <c r="G84" s="228"/>
+      <c r="H84" s="228"/>
+      <c r="I84" s="229"/>
+      <c r="J84" s="230"/>
     </row>
     <row r="85" s="3" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A85" s="233" t="s">
+      <c r="A85" s="231" t="s">
         <v>113</v>
       </c>
-      <c r="B85" s="234"/>
-      <c r="C85" s="233" t="s">
+      <c r="B85" s="232"/>
+      <c r="C85" s="231" t="s">
         <v>114</v>
       </c>
-      <c r="D85" s="233" t="s">
+      <c r="D85" s="231" t="s">
         <v>115</v>
       </c>
-      <c r="E85" s="235"/>
-      <c r="F85" s="235"/>
-      <c r="G85" s="235"/>
-      <c r="H85" s="235"/>
-      <c r="I85" s="234"/>
+      <c r="E85" s="233"/>
+      <c r="F85" s="233"/>
+      <c r="G85" s="233"/>
+      <c r="H85" s="233"/>
+      <c r="I85" s="232"/>
     </row>
     <row r="86" s="3" customFormat="1" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A86" s="236" t="s">
+      <c r="A86" s="234" t="s">
         <v>116</v>
       </c>
-      <c r="B86" s="237"/>
-      <c r="C86" s="238" t="s">
+      <c r="B86" s="235"/>
+      <c r="C86" s="236" t="s">
         <v>116</v>
       </c>
-      <c r="D86" s="239" t="s">
+      <c r="D86" s="237" t="s">
         <v>116</v>
       </c>
-      <c r="E86" s="240"/>
-      <c r="F86" s="240"/>
-      <c r="G86" s="240"/>
-      <c r="H86" s="240"/>
-      <c r="I86" s="241"/>
+      <c r="E86" s="238"/>
+      <c r="F86" s="238"/>
+      <c r="G86" s="238"/>
+      <c r="H86" s="238"/>
+      <c r="I86" s="239"/>
     </row>
     <row r="87" s="2" customFormat="1" ht="12.75" customHeight="1" spans="1:10">
-      <c r="A87" s="242" t="s">
+      <c r="A87" s="240" t="s">
         <v>117</v>
       </c>
-      <c r="B87" s="243"/>
+      <c r="B87" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="92">
@@ -5712,7 +5706,7 @@
     <mergeCell ref="F63:I64"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="256" scale="42" orientation="portrait"/>
+  <pageSetup paperSize="256" scale="43" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
